--- a/database/seeders/data/Manual de interação Droga Nutriente-1.xlsx
+++ b/database/seeders/data/Manual de interação Droga Nutriente-1.xlsx
@@ -21,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="1156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="1157">
   <si>
     <t xml:space="preserve">Nome Comercial</t>
   </si>
   <si>
-    <t>Fármaco</t>
+    <t>fármaco</t>
   </si>
   <si>
     <t>Classificação</t>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">Alterações laboratoriais</t>
   </si>
   <si>
-    <t xml:space="preserve">Ação com os médicos</t>
-  </si>
-  <si>
-    <t>Observação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ação com a Nutrição</t>
+    <t xml:space="preserve">ação com os médicos</t>
+  </si>
+  <si>
+    <t>observações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ação com a nutrição</t>
   </si>
   <si>
     <t xml:space="preserve">ação com a enfermagem </t>
@@ -8995,6 +8995,9 @@
   </si>
   <si>
     <t xml:space="preserve">Farmaceutica Responsavél:</t>
+  </si>
+  <si>
+    <t>Fármaco</t>
   </si>
   <si>
     <t>Nutrição</t>
@@ -19019,7 +19022,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>1</v>
+        <v>1151</v>
       </c>
       <c r="C11" s="40" t="s">
         <v>4</v>
@@ -19028,13 +19031,13 @@
         <v>3</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="12" ht="215.09999999999999" customHeight="1">
@@ -19282,7 +19285,7 @@
     </row>
     <row r="21">
       <c r="A21" s="42" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B21" s="43"/>
       <c r="C21" s="43"/>
@@ -19364,7 +19367,7 @@
   <sheetData>
     <row r="1" ht="60">
       <c r="A1" s="51" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
   </sheetData>

--- a/database/seeders/data/Manual de interação Droga Nutriente-1.xlsx
+++ b/database/seeders/data/Manual de interação Droga Nutriente-1.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">ação com a nutrição</t>
   </si>
   <si>
-    <t xml:space="preserve">ação com a enfermagem </t>
+    <t xml:space="preserve">ação com a enfermagem</t>
   </si>
   <si>
     <t xml:space="preserve">Fluimucil 10% ampola 3ml                      </t>
@@ -19349,7 +19349,7 @@
     </dataValidation>
   </dataValidations>
   <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.51000000000000012" right="0.23000000000000004" top="0.40314960629921276" bottom="0.39629921259842521" header="0.31" footer="0.31"/>
+  <pageMargins left="0.51000000000000023" right="0.23000000000000004" top="0.40314960629921281" bottom="0.39629921259842521" header="0.31" footer="0.31"/>
   <pageSetup paperSize="9" scale="70" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter>
     <oddFooter>&amp;CHOSPITAL DAHER</oddFooter>
@@ -19372,7 +19372,7 @@
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157500000008" bottom="0.78740157500000008" header="0.31496062000000008" footer="0.31496062000000008"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157500000008" bottom="0.78740157500000008" header="0.31496062000000014" footer="0.31496062000000014"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
